--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,9 +319,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:capacityAvailable</t>
   </si>
   <si>
@@ -366,6 +363,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:capacityAvailable.value[x]</t>
@@ -1307,24 +1307,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1349,10 +1349,10 @@
         <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1412,7 +1412,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1558,7 +1558,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1618,7 +1618,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1655,16 +1655,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1714,22 +1714,22 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1826,13 +1826,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -1871,7 +1871,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1931,7 +1931,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1945,7 +1945,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2048,7 +2048,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2137,7 +2137,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2151,7 +2151,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2174,16 +2174,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2233,22 +2233,22 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2345,13 +2345,13 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -2390,7 +2390,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2450,7 +2450,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2464,7 +2464,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2567,7 +2567,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2596,7 +2596,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2656,7 +2656,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2670,7 +2670,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2693,16 +2693,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2752,22 +2752,22 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2864,13 +2864,13 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
@@ -2909,7 +2909,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2969,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -2983,7 +2983,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3086,7 +3086,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3175,7 +3175,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3189,7 +3189,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3212,16 +3212,16 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3271,22 +3271,22 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -3383,13 +3383,13 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -3428,7 +3428,7 @@
         <v>145</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3488,7 +3488,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3502,7 +3502,7 @@
         <v>146</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3605,7 +3605,7 @@
         <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3694,7 +3694,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3708,7 +3708,7 @@
         <v>148</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3731,16 +3731,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3790,22 +3790,22 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="29">
@@ -3902,13 +3902,13 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30">
@@ -3947,7 +3947,7 @@
         <v>152</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4007,7 +4007,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4021,7 +4021,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4124,7 +4124,7 @@
         <v>154</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4153,7 +4153,7 @@
         <v>30</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4213,7 +4213,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4227,7 +4227,7 @@
         <v>155</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4250,16 +4250,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4309,22 +4309,22 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="34">
@@ -4421,13 +4421,13 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
@@ -4466,7 +4466,7 @@
         <v>159</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4526,7 +4526,7 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>81</v>
@@ -4540,7 +4540,7 @@
         <v>160</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4643,7 +4643,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4672,7 +4672,7 @@
         <v>30</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4732,7 +4732,7 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>81</v>
@@ -4746,7 +4746,7 @@
         <v>162</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4769,16 +4769,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4828,22 +4828,22 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="39">
@@ -4940,13 +4940,13 @@
         <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40">
@@ -4985,7 +4985,7 @@
         <v>166</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5045,7 +5045,7 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>81</v>
@@ -5059,7 +5059,7 @@
         <v>167</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5162,7 +5162,7 @@
         <v>168</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5191,7 +5191,7 @@
         <v>30</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5251,7 +5251,7 @@
         <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>81</v>
@@ -5265,7 +5265,7 @@
         <v>169</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5288,16 +5288,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5347,22 +5347,22 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="44">
@@ -5459,21 +5459,21 @@
         <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5496,16 +5496,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5555,22 +5555,22 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="46">
@@ -5667,13 +5667,13 @@
         <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,6 +319,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:capacityAvailable</t>
   </si>
   <si>
@@ -363,9 +366,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:capacityAvailable.value[x]</t>
@@ -1307,24 +1307,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1349,10 +1349,10 @@
         <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1412,7 +1412,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1558,7 +1558,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1618,7 +1618,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1655,16 +1655,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1714,7 +1714,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1729,7 +1729,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1826,13 +1826,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1871,7 +1871,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1931,7 +1931,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1945,7 +1945,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2048,7 +2048,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2137,7 +2137,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2151,7 +2151,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2174,16 +2174,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2233,7 +2233,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2248,7 +2248,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2345,13 +2345,13 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -2390,7 +2390,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2450,7 +2450,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2464,7 +2464,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2567,7 +2567,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2596,7 +2596,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2656,7 +2656,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2670,7 +2670,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2693,16 +2693,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2752,7 +2752,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -2767,7 +2767,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2864,13 +2864,13 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
@@ -2909,7 +2909,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2969,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -2983,7 +2983,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3086,7 +3086,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3175,7 +3175,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3189,7 +3189,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3212,16 +3212,16 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3271,7 +3271,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -3286,7 +3286,7 @@
         <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -3383,13 +3383,13 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25">
@@ -3428,7 +3428,7 @@
         <v>145</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3488,7 +3488,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3502,7 +3502,7 @@
         <v>146</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3605,7 +3605,7 @@
         <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3694,7 +3694,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3708,7 +3708,7 @@
         <v>148</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3731,16 +3731,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3790,7 +3790,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -3805,7 +3805,7 @@
         <v>76</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
@@ -3902,13 +3902,13 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -3947,7 +3947,7 @@
         <v>152</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4007,7 +4007,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4021,7 +4021,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4124,7 +4124,7 @@
         <v>154</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4153,7 +4153,7 @@
         <v>30</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4213,7 +4213,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4227,7 +4227,7 @@
         <v>155</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4250,16 +4250,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4309,7 +4309,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -4324,7 +4324,7 @@
         <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
@@ -4421,13 +4421,13 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -4466,7 +4466,7 @@
         <v>159</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4526,7 +4526,7 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>81</v>
@@ -4540,7 +4540,7 @@
         <v>160</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4643,7 +4643,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4672,7 +4672,7 @@
         <v>30</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4732,7 +4732,7 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>81</v>
@@ -4746,7 +4746,7 @@
         <v>162</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4769,16 +4769,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4828,7 +4828,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -4843,7 +4843,7 @@
         <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
@@ -4940,13 +4940,13 @@
         <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40">
@@ -4985,7 +4985,7 @@
         <v>166</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5045,7 +5045,7 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>81</v>
@@ -5059,7 +5059,7 @@
         <v>167</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5162,7 +5162,7 @@
         <v>168</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5191,7 +5191,7 @@
         <v>30</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5251,7 +5251,7 @@
         <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>81</v>
@@ -5265,7 +5265,7 @@
         <v>169</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5288,16 +5288,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5347,7 +5347,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -5362,7 +5362,7 @@
         <v>76</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44">
@@ -5459,21 +5459,21 @@
         <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5496,16 +5496,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5555,7 +5555,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -5570,7 +5570,7 @@
         <v>76</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46">
@@ -5667,13 +5667,13 @@
         <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,9 +319,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:capacityAvailable</t>
   </si>
   <si>
@@ -366,6 +363,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:capacityAvailable.value[x]</t>
@@ -1307,24 +1307,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1349,10 +1349,10 @@
         <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1412,7 +1412,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1558,7 +1558,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1618,7 +1618,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1655,16 +1655,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1714,22 +1714,22 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1826,13 +1826,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -1871,7 +1871,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1931,7 +1931,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1945,7 +1945,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2048,7 +2048,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2137,7 +2137,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2151,7 +2151,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2174,16 +2174,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2233,22 +2233,22 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2345,13 +2345,13 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -2390,7 +2390,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2450,7 +2450,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2464,7 +2464,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2567,7 +2567,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2596,7 +2596,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2656,7 +2656,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2670,7 +2670,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2693,16 +2693,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2752,22 +2752,22 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2864,13 +2864,13 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
@@ -2909,7 +2909,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2969,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -2983,7 +2983,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3086,7 +3086,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3175,7 +3175,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3189,7 +3189,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3212,16 +3212,16 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3271,22 +3271,22 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -3383,13 +3383,13 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -3428,7 +3428,7 @@
         <v>145</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3488,7 +3488,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3502,7 +3502,7 @@
         <v>146</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3605,7 +3605,7 @@
         <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3694,7 +3694,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3708,7 +3708,7 @@
         <v>148</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3731,16 +3731,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3790,22 +3790,22 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="29">
@@ -3902,13 +3902,13 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30">
@@ -3947,7 +3947,7 @@
         <v>152</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4007,7 +4007,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4021,7 +4021,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4124,7 +4124,7 @@
         <v>154</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4153,7 +4153,7 @@
         <v>30</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4213,7 +4213,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4227,7 +4227,7 @@
         <v>155</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4250,16 +4250,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4309,22 +4309,22 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="34">
@@ -4421,13 +4421,13 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
@@ -4466,7 +4466,7 @@
         <v>159</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4526,7 +4526,7 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>81</v>
@@ -4540,7 +4540,7 @@
         <v>160</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4643,7 +4643,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4672,7 +4672,7 @@
         <v>30</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4732,7 +4732,7 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>81</v>
@@ -4746,7 +4746,7 @@
         <v>162</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4769,16 +4769,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4828,22 +4828,22 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="39">
@@ -4940,13 +4940,13 @@
         <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40">
@@ -4985,7 +4985,7 @@
         <v>166</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5045,7 +5045,7 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>81</v>
@@ -5059,7 +5059,7 @@
         <v>167</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5162,7 +5162,7 @@
         <v>168</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5191,7 +5191,7 @@
         <v>30</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5251,7 +5251,7 @@
         <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>81</v>
@@ -5265,7 +5265,7 @@
         <v>169</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5288,16 +5288,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5347,22 +5347,22 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="44">
@@ -5459,21 +5459,21 @@
         <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5496,16 +5496,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5555,22 +5555,22 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="46">
@@ -5667,13 +5667,13 @@
         <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,6 +319,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:capacityAvailable</t>
   </si>
   <si>
@@ -363,9 +366,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:capacityAvailable.value[x]</t>
@@ -1307,24 +1307,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1349,10 +1349,10 @@
         <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1412,7 +1412,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1558,7 +1558,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1618,7 +1618,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1655,16 +1655,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1714,7 +1714,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1729,7 +1729,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1826,13 +1826,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1871,7 +1871,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1931,7 +1931,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1945,7 +1945,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2048,7 +2048,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2137,7 +2137,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2151,7 +2151,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2174,16 +2174,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2233,7 +2233,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2248,7 +2248,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2345,13 +2345,13 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -2390,7 +2390,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2450,7 +2450,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2464,7 +2464,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2567,7 +2567,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2596,7 +2596,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2656,7 +2656,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2670,7 +2670,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2693,16 +2693,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2752,7 +2752,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -2767,7 +2767,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2864,13 +2864,13 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
@@ -2909,7 +2909,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2969,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -2983,7 +2983,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3086,7 +3086,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3175,7 +3175,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3189,7 +3189,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3212,16 +3212,16 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3271,7 +3271,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -3286,7 +3286,7 @@
         <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -3383,13 +3383,13 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25">
@@ -3428,7 +3428,7 @@
         <v>145</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3488,7 +3488,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3502,7 +3502,7 @@
         <v>146</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3605,7 +3605,7 @@
         <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3694,7 +3694,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3708,7 +3708,7 @@
         <v>148</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3731,16 +3731,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3790,7 +3790,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -3805,7 +3805,7 @@
         <v>76</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
@@ -3902,13 +3902,13 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -3947,7 +3947,7 @@
         <v>152</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4007,7 +4007,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4021,7 +4021,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4124,7 +4124,7 @@
         <v>154</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4153,7 +4153,7 @@
         <v>30</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4213,7 +4213,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4227,7 +4227,7 @@
         <v>155</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4250,16 +4250,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4309,7 +4309,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -4324,7 +4324,7 @@
         <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
@@ -4421,13 +4421,13 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -4466,7 +4466,7 @@
         <v>159</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4526,7 +4526,7 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>81</v>
@@ -4540,7 +4540,7 @@
         <v>160</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4643,7 +4643,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4672,7 +4672,7 @@
         <v>30</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4732,7 +4732,7 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>81</v>
@@ -4746,7 +4746,7 @@
         <v>162</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4769,16 +4769,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4828,7 +4828,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -4843,7 +4843,7 @@
         <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
@@ -4940,13 +4940,13 @@
         <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40">
@@ -4985,7 +4985,7 @@
         <v>166</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5045,7 +5045,7 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>81</v>
@@ -5059,7 +5059,7 @@
         <v>167</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5162,7 +5162,7 @@
         <v>168</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5191,7 +5191,7 @@
         <v>30</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5251,7 +5251,7 @@
         <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>81</v>
@@ -5265,7 +5265,7 @@
         <v>169</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5288,16 +5288,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5347,7 +5347,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -5362,7 +5362,7 @@
         <v>76</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44">
@@ -5459,21 +5459,21 @@
         <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5496,16 +5496,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5555,7 +5555,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -5570,7 +5570,7 @@
         <v>76</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46">
@@ -5667,13 +5667,13 @@
         <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
+++ b/main/ig/StructureDefinition-as-ext-supported-capacity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
